--- a/artfynd/A 35457-2024 artfynd.xlsx
+++ b/artfynd/A 35457-2024 artfynd.xlsx
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125873437</v>
+        <v>125872990</v>
       </c>
       <c r="B10" t="n">
-        <v>78725</v>
+        <v>78634</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458918</v>
+        <v>458898</v>
       </c>
       <c r="R10" t="n">
-        <v>6840939</v>
+        <v>6840910</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125872990</v>
+        <v>125873437</v>
       </c>
       <c r="B11" t="n">
-        <v>78634</v>
+        <v>78725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458898</v>
+        <v>458918</v>
       </c>
       <c r="R11" t="n">
-        <v>6840910</v>
+        <v>6840939</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35457-2024 artfynd.xlsx
+++ b/artfynd/A 35457-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125873077</v>
+        <v>125873185</v>
       </c>
       <c r="B2" t="n">
-        <v>78634</v>
+        <v>78726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458904</v>
+        <v>458924</v>
       </c>
       <c r="R2" t="n">
-        <v>6840900</v>
+        <v>6840898</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125873185</v>
+        <v>125873077</v>
       </c>
       <c r="B3" t="n">
-        <v>78725</v>
+        <v>78635</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458924</v>
+        <v>458904</v>
       </c>
       <c r="R3" t="n">
-        <v>6840898</v>
+        <v>6840900</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>125873645</v>
       </c>
       <c r="B4" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125873031</v>
       </c>
       <c r="B5" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125873231</v>
       </c>
       <c r="B6" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125872857</v>
       </c>
       <c r="B7" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125873709</v>
       </c>
       <c r="B8" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125873442</v>
       </c>
       <c r="B9" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125872990</v>
+        <v>125873437</v>
       </c>
       <c r="B10" t="n">
-        <v>78634</v>
+        <v>78726</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458898</v>
+        <v>458918</v>
       </c>
       <c r="R10" t="n">
-        <v>6840910</v>
+        <v>6840939</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125873437</v>
+        <v>125872990</v>
       </c>
       <c r="B11" t="n">
-        <v>78725</v>
+        <v>78635</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458918</v>
+        <v>458898</v>
       </c>
       <c r="R11" t="n">
-        <v>6840939</v>
+        <v>6840910</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>125873832</v>
       </c>
       <c r="B12" t="n">
-        <v>79062</v>
+        <v>79063</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 35457-2024 artfynd.xlsx
+++ b/artfynd/A 35457-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125873185</v>
+        <v>125873077</v>
       </c>
       <c r="B2" t="n">
-        <v>78726</v>
+        <v>78635</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458924</v>
+        <v>458904</v>
       </c>
       <c r="R2" t="n">
-        <v>6840898</v>
+        <v>6840900</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125873077</v>
+        <v>125873185</v>
       </c>
       <c r="B3" t="n">
-        <v>78635</v>
+        <v>78726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458904</v>
+        <v>458924</v>
       </c>
       <c r="R3" t="n">
-        <v>6840900</v>
+        <v>6840898</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 35457-2024 artfynd.xlsx
+++ b/artfynd/A 35457-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125873077</v>
       </c>
       <c r="B2" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125873185</v>
       </c>
       <c r="B3" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125873645</v>
       </c>
       <c r="B4" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125873031</v>
       </c>
       <c r="B5" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125873231</v>
       </c>
       <c r="B6" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125872857</v>
       </c>
       <c r="B7" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125873709</v>
       </c>
       <c r="B8" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125873442</v>
       </c>
       <c r="B9" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125873437</v>
+        <v>125872990</v>
       </c>
       <c r="B10" t="n">
-        <v>78726</v>
+        <v>78639</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458918</v>
+        <v>458898</v>
       </c>
       <c r="R10" t="n">
-        <v>6840939</v>
+        <v>6840910</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125872990</v>
+        <v>125873437</v>
       </c>
       <c r="B11" t="n">
-        <v>78635</v>
+        <v>78730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458898</v>
+        <v>458918</v>
       </c>
       <c r="R11" t="n">
-        <v>6840910</v>
+        <v>6840939</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>125873832</v>
       </c>
       <c r="B12" t="n">
-        <v>79063</v>
+        <v>79067</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 35457-2024 artfynd.xlsx
+++ b/artfynd/A 35457-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125873077</v>
       </c>
       <c r="B2" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125873185</v>
       </c>
       <c r="B3" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125873645</v>
       </c>
       <c r="B4" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125873031</v>
       </c>
       <c r="B5" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125873231</v>
       </c>
       <c r="B6" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125872857</v>
       </c>
       <c r="B7" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125873709</v>
       </c>
       <c r="B8" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125873442</v>
       </c>
       <c r="B9" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125872990</v>
+        <v>125873437</v>
       </c>
       <c r="B10" t="n">
-        <v>78639</v>
+        <v>78731</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458898</v>
+        <v>458918</v>
       </c>
       <c r="R10" t="n">
-        <v>6840910</v>
+        <v>6840939</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125873437</v>
+        <v>125872990</v>
       </c>
       <c r="B11" t="n">
-        <v>78730</v>
+        <v>78640</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458918</v>
+        <v>458898</v>
       </c>
       <c r="R11" t="n">
-        <v>6840939</v>
+        <v>6840910</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>125873832</v>
       </c>
       <c r="B12" t="n">
-        <v>79067</v>
+        <v>79068</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 35457-2024 artfynd.xlsx
+++ b/artfynd/A 35457-2024 artfynd.xlsx
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125873437</v>
+        <v>125872990</v>
       </c>
       <c r="B10" t="n">
-        <v>78731</v>
+        <v>78640</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458918</v>
+        <v>458898</v>
       </c>
       <c r="R10" t="n">
-        <v>6840939</v>
+        <v>6840910</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125872990</v>
+        <v>125873437</v>
       </c>
       <c r="B11" t="n">
-        <v>78640</v>
+        <v>78731</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458898</v>
+        <v>458918</v>
       </c>
       <c r="R11" t="n">
-        <v>6840910</v>
+        <v>6840939</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35457-2024 artfynd.xlsx
+++ b/artfynd/A 35457-2024 artfynd.xlsx
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125872990</v>
+        <v>125873437</v>
       </c>
       <c r="B10" t="n">
-        <v>78640</v>
+        <v>78731</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458898</v>
+        <v>458918</v>
       </c>
       <c r="R10" t="n">
-        <v>6840910</v>
+        <v>6840939</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125873437</v>
+        <v>125872990</v>
       </c>
       <c r="B11" t="n">
-        <v>78731</v>
+        <v>78640</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458918</v>
+        <v>458898</v>
       </c>
       <c r="R11" t="n">
-        <v>6840939</v>
+        <v>6840910</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35457-2024 artfynd.xlsx
+++ b/artfynd/A 35457-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125873077</v>
       </c>
       <c r="B2" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125873185</v>
       </c>
       <c r="B3" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125873645</v>
       </c>
       <c r="B4" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125873031</v>
       </c>
       <c r="B5" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125873231</v>
       </c>
       <c r="B6" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125872857</v>
       </c>
       <c r="B7" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125873709</v>
       </c>
       <c r="B8" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125873442</v>
       </c>
       <c r="B9" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125873437</v>
+        <v>125872990</v>
       </c>
       <c r="B10" t="n">
-        <v>78731</v>
+        <v>78644</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458918</v>
+        <v>458898</v>
       </c>
       <c r="R10" t="n">
-        <v>6840939</v>
+        <v>6840910</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125872990</v>
+        <v>125873437</v>
       </c>
       <c r="B11" t="n">
-        <v>78640</v>
+        <v>78735</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458898</v>
+        <v>458918</v>
       </c>
       <c r="R11" t="n">
-        <v>6840910</v>
+        <v>6840939</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>125873832</v>
       </c>
       <c r="B12" t="n">
-        <v>79068</v>
+        <v>79072</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 35457-2024 artfynd.xlsx
+++ b/artfynd/A 35457-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125873077</v>
+        <v>125873185</v>
       </c>
       <c r="B2" t="n">
-        <v>78644</v>
+        <v>78735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458904</v>
+        <v>458924</v>
       </c>
       <c r="R2" t="n">
-        <v>6840900</v>
+        <v>6840898</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125873185</v>
+        <v>125873077</v>
       </c>
       <c r="B3" t="n">
-        <v>78735</v>
+        <v>78644</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458924</v>
+        <v>458904</v>
       </c>
       <c r="R3" t="n">
-        <v>6840898</v>
+        <v>6840900</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125872990</v>
+        <v>125873437</v>
       </c>
       <c r="B10" t="n">
-        <v>78644</v>
+        <v>78735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458898</v>
+        <v>458918</v>
       </c>
       <c r="R10" t="n">
-        <v>6840910</v>
+        <v>6840939</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125873437</v>
+        <v>125872990</v>
       </c>
       <c r="B11" t="n">
-        <v>78735</v>
+        <v>78644</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458918</v>
+        <v>458898</v>
       </c>
       <c r="R11" t="n">
-        <v>6840939</v>
+        <v>6840910</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35457-2024 artfynd.xlsx
+++ b/artfynd/A 35457-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125873185</v>
+        <v>125873077</v>
       </c>
       <c r="B2" t="n">
-        <v>78735</v>
+        <v>78644</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458924</v>
+        <v>458904</v>
       </c>
       <c r="R2" t="n">
-        <v>6840898</v>
+        <v>6840900</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125873077</v>
+        <v>125873185</v>
       </c>
       <c r="B3" t="n">
-        <v>78644</v>
+        <v>78735</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458904</v>
+        <v>458924</v>
       </c>
       <c r="R3" t="n">
-        <v>6840900</v>
+        <v>6840898</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 35457-2024 artfynd.xlsx
+++ b/artfynd/A 35457-2024 artfynd.xlsx
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125873437</v>
+        <v>125872990</v>
       </c>
       <c r="B10" t="n">
-        <v>78735</v>
+        <v>78644</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458918</v>
+        <v>458898</v>
       </c>
       <c r="R10" t="n">
-        <v>6840939</v>
+        <v>6840910</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125872990</v>
+        <v>125873437</v>
       </c>
       <c r="B11" t="n">
-        <v>78644</v>
+        <v>78735</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458898</v>
+        <v>458918</v>
       </c>
       <c r="R11" t="n">
-        <v>6840910</v>
+        <v>6840939</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35457-2024 artfynd.xlsx
+++ b/artfynd/A 35457-2024 artfynd.xlsx
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125872990</v>
+        <v>125873437</v>
       </c>
       <c r="B10" t="n">
-        <v>78644</v>
+        <v>78735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458898</v>
+        <v>458918</v>
       </c>
       <c r="R10" t="n">
-        <v>6840910</v>
+        <v>6840939</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125873437</v>
+        <v>125872990</v>
       </c>
       <c r="B11" t="n">
-        <v>78735</v>
+        <v>78644</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458918</v>
+        <v>458898</v>
       </c>
       <c r="R11" t="n">
-        <v>6840939</v>
+        <v>6840910</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35457-2024 artfynd.xlsx
+++ b/artfynd/A 35457-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125873077</v>
+        <v>125873185</v>
       </c>
       <c r="B2" t="n">
-        <v>78644</v>
+        <v>78738</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458904</v>
+        <v>458924</v>
       </c>
       <c r="R2" t="n">
-        <v>6840900</v>
+        <v>6840898</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125873185</v>
+        <v>125873077</v>
       </c>
       <c r="B3" t="n">
-        <v>78735</v>
+        <v>78647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458924</v>
+        <v>458904</v>
       </c>
       <c r="R3" t="n">
-        <v>6840898</v>
+        <v>6840900</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>125873645</v>
       </c>
       <c r="B4" t="n">
-        <v>78644</v>
+        <v>78647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125873031</v>
       </c>
       <c r="B5" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125873231</v>
       </c>
       <c r="B6" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125872857</v>
       </c>
       <c r="B7" t="n">
-        <v>78644</v>
+        <v>78647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125873709</v>
       </c>
       <c r="B8" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125873442</v>
       </c>
       <c r="B9" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125873437</v>
+        <v>125872990</v>
       </c>
       <c r="B10" t="n">
-        <v>78735</v>
+        <v>78647</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458918</v>
+        <v>458898</v>
       </c>
       <c r="R10" t="n">
-        <v>6840939</v>
+        <v>6840910</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125872990</v>
+        <v>125873437</v>
       </c>
       <c r="B11" t="n">
-        <v>78644</v>
+        <v>78738</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458898</v>
+        <v>458918</v>
       </c>
       <c r="R11" t="n">
-        <v>6840910</v>
+        <v>6840939</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>125873832</v>
       </c>
       <c r="B12" t="n">
-        <v>79072</v>
+        <v>79075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 35457-2024 artfynd.xlsx
+++ b/artfynd/A 35457-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125873185</v>
+        <v>125873077</v>
       </c>
       <c r="B2" t="n">
-        <v>78738</v>
+        <v>78647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458924</v>
+        <v>458904</v>
       </c>
       <c r="R2" t="n">
-        <v>6840898</v>
+        <v>6840900</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125873077</v>
+        <v>125873185</v>
       </c>
       <c r="B3" t="n">
-        <v>78647</v>
+        <v>78738</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458904</v>
+        <v>458924</v>
       </c>
       <c r="R3" t="n">
-        <v>6840900</v>
+        <v>6840898</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125872990</v>
+        <v>125873437</v>
       </c>
       <c r="B10" t="n">
-        <v>78647</v>
+        <v>78738</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458898</v>
+        <v>458918</v>
       </c>
       <c r="R10" t="n">
-        <v>6840910</v>
+        <v>6840939</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125873437</v>
+        <v>125872990</v>
       </c>
       <c r="B11" t="n">
-        <v>78738</v>
+        <v>78647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458918</v>
+        <v>458898</v>
       </c>
       <c r="R11" t="n">
-        <v>6840939</v>
+        <v>6840910</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 35457-2024 artfynd.xlsx
+++ b/artfynd/A 35457-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125873077</v>
+        <v>125872857</v>
       </c>
       <c r="B2" t="n">
-        <v>78647</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458904</v>
+        <v>458871</v>
       </c>
       <c r="R2" t="n">
-        <v>6840900</v>
+        <v>6840916</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125873185</v>
+        <v>125872990</v>
       </c>
       <c r="B3" t="n">
-        <v>78738</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458924</v>
+        <v>458898</v>
       </c>
       <c r="R3" t="n">
-        <v>6840898</v>
+        <v>6840910</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125873645</v>
+        <v>125873077</v>
       </c>
       <c r="B4" t="n">
-        <v>78647</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458936</v>
+        <v>458904</v>
       </c>
       <c r="R4" t="n">
-        <v>6840972</v>
+        <v>6840900</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125873031</v>
+        <v>125873645</v>
       </c>
       <c r="B5" t="n">
-        <v>78739</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458903</v>
+        <v>458936</v>
       </c>
       <c r="R5" t="n">
-        <v>6840910</v>
+        <v>6840972</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125873231</v>
+        <v>125873832</v>
       </c>
       <c r="B6" t="n">
-        <v>78739</v>
+        <v>79422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458911</v>
+        <v>458914</v>
       </c>
       <c r="R6" t="n">
-        <v>6840912</v>
+        <v>6841026</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125872857</v>
+        <v>125873185</v>
       </c>
       <c r="B7" t="n">
-        <v>78647</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458871</v>
+        <v>458924</v>
       </c>
       <c r="R7" t="n">
-        <v>6840916</v>
+        <v>6840898</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125873709</v>
+        <v>125873437</v>
       </c>
       <c r="B8" t="n">
-        <v>78739</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458931</v>
+        <v>458918</v>
       </c>
       <c r="R8" t="n">
-        <v>6841009</v>
+        <v>6840939</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125873442</v>
+        <v>125873031</v>
       </c>
       <c r="B9" t="n">
-        <v>78739</v>
+        <v>79085</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458916</v>
+        <v>458903</v>
       </c>
       <c r="R9" t="n">
-        <v>6840928</v>
+        <v>6840910</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125873437</v>
+        <v>125873231</v>
       </c>
       <c r="B10" t="n">
-        <v>78738</v>
+        <v>79085</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458918</v>
+        <v>458911</v>
       </c>
       <c r="R10" t="n">
-        <v>6840939</v>
+        <v>6840912</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125872990</v>
+        <v>125873442</v>
       </c>
       <c r="B11" t="n">
-        <v>78647</v>
+        <v>79085</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458898</v>
+        <v>458916</v>
       </c>
       <c r="R11" t="n">
-        <v>6840910</v>
+        <v>6840928</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125873832</v>
+        <v>125873709</v>
       </c>
       <c r="B12" t="n">
-        <v>79075</v>
+        <v>79085</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458914</v>
+        <v>458931</v>
       </c>
       <c r="R12" t="n">
-        <v>6841026</v>
+        <v>6841009</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1739,6 +1739,103 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125874303</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lillberget, Lillberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>458938</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6840852</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35457-2024 artfynd.xlsx
+++ b/artfynd/A 35457-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125872857</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125872990</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125873077</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125873645</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125873832</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125873185</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125873437</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125873031</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125873231</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125873442</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125873709</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,8 +1896,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125874303</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>